--- a/InputData/elec/MCF/Maximum Capacity Factor.xlsx
+++ b/InputData/elec/MCF/Maximum Capacity Factor.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27126"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\robbie\Dropbox (Energy Innovation)\My Documents\Energy Policy Solutions\US\Models\eps-us\InputData\elec\MCF\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\TX\elec\MCF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF5E761-3510-4551-BBBD-14D4B578101B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74DE36F8-A4DD-4AAE-8515-3B1FC2FBB980}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="12645" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="12" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="37">
   <si>
     <t>nuclear</t>
   </si>
@@ -161,15 +161,15 @@
   </si>
   <si>
     <t>in any given hour. This is used for non-variable plant types, including hydro. We apply</t>
+  </si>
+  <si>
+    <t>Texas</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -322,13 +322,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -336,6 +335,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="11">
     <cellStyle name="Body: normal cell" xfId="5" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -769,6 +769,12 @@
       <c r="A1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="B1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C1" s="8">
+        <v>45320</v>
+      </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="2"/>
@@ -801,7 +807,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="1"/>
@@ -826,7 +832,7 @@
       <c r="A10" t="s">
         <v>35</v>
       </c>
-      <c r="H10" s="4"/>
+      <c r="H10" s="3"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -864,231 +870,214 @@
     <tabColor rgb="FF002060"/>
   </sheetPr>
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.42578125" customWidth="1"/>
     <col min="2" max="3" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="4" t="s">
         <v>16</v>
       </c>
       <c r="B1" s="5"/>
-      <c r="C1" s="7"/>
+      <c r="C1" s="6"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="3">
+      <c r="B2">
         <v>0.85</v>
       </c>
-      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C3" s="3"/>
+      <c r="B3">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C4" s="3"/>
+      <c r="B4">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="3">
-        <v>0.91</v>
-      </c>
-      <c r="C5" s="3"/>
+      <c r="B5">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C6" s="3"/>
+      <c r="B6">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="C7" s="3"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="C8" s="3"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>3</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="C9" s="3"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C10" s="3"/>
+      <c r="B10">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C11" s="3"/>
+      <c r="B11">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C12" s="3"/>
+      <c r="B12">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C13" s="3"/>
+      <c r="B13">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C14" s="3"/>
+      <c r="B14">
+        <v>0.95</v>
+      </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="3">
+      <c r="B15">
         <v>0</v>
       </c>
-      <c r="C15" s="3"/>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C16" s="3"/>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
-      <c r="B17" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C17" s="3"/>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="3">
-        <v>0.95</v>
-      </c>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B19" s="3">
+      <c r="B19">
         <f>B2</f>
         <v>0.85</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="3">
+      <c r="B20">
         <f>B4</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>29</v>
       </c>
-      <c r="B21" s="3">
+      <c r="B21">
         <f>B10</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>30</v>
       </c>
-      <c r="B22" s="3">
+      <c r="B22">
         <f>B14</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="3">
+      <c r="B23">
         <f>B5</f>
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B24" s="3">
+      <c r="B24">
         <f>B4</f>
         <v>0.95</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B25" s="3">
+      <c r="B25">
         <f>B4</f>
         <v>0.95</v>
       </c>
